--- a/Docs/ISIS1225-TablasDatosReto2.xlsx
+++ b/Docs/ISIS1225-TablasDatosReto2.xlsx
@@ -1,37 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Lina/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f37e920cb68ed4a8/Desktop/Reto2-G03/Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{4A5DBDDE-59DE-4983-A5DD-216DD4370536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBD65B10-B751-40ED-8957-A37F9DC21957}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{4A5DBDDE-59DE-4983-A5DD-216DD4370536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CE162CA-726A-4580-81E1-998AC705562F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
   </bookViews>
   <sheets>
     <sheet name="01-Data Req. 4" sheetId="1" r:id="rId1"/>
     <sheet name="02-Gráfica Req. 4" sheetId="8" r:id="rId2"/>
     <sheet name="03-Análisis Req. 4" sheetId="9" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -107,7 +99,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,6 +141,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -207,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -233,6 +233,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -681,7 +682,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES_tradnl"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -748,7 +749,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -841,7 +842,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
+                  <a:endParaRPr lang="es-CO"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -895,31 +896,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>9.3816000000000006</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>28.8857</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>51.407699999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>85.055099999999996</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>127.274</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1014,7 +1015,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
+                  <a:endParaRPr lang="es-CO"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -1192,7 +1193,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="es-CO"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1230,7 +1231,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1328121328"/>
@@ -1309,7 +1310,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="es-CO"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1347,7 +1348,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1328118000"/>
@@ -1389,13 +1390,12 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1403,6 +1403,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1426,7 +1427,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="es-CO"/>
     </a:p>
   </c:txPr>
 </c:chartSpace>
@@ -2092,9 +2093,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2132,7 +2133,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2238,7 +2239,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2380,7 +2381,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2388,18 +2389,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B14742-4EBB-4241-AC8A-0E5F24F7BB7B}">
-  <dimension ref="A1:H26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="19.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="24.5" customWidth="1"/>
+    <col min="1" max="1" width="19.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="24.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.25" customHeight="1">
+    <row r="1" spans="1:9" ht="14.25" customHeight="1">
       <c r="C1" s="9" t="s">
         <v>0</v>
       </c>
@@ -2409,7 +2410,7 @@
       <c r="G1" s="9"/>
       <c r="H1" s="9"/>
     </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="32">
+    <row r="2" spans="1:9" s="5" customFormat="1" ht="28">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2435,7 +2436,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="5" customFormat="1">
+    <row r="3" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A3" s="2">
         <v>0.1</v>
       </c>
@@ -2463,7 +2464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="5" customFormat="1">
+    <row r="4" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A4" s="2">
         <v>0.2</v>
       </c>
@@ -2472,26 +2473,26 @@
         <v>20000</v>
       </c>
       <c r="C4" s="3">
-        <v>0</v>
+        <v>9.3816000000000006</v>
       </c>
       <c r="D4" s="3">
-        <v>0</v>
+        <v>11.7384</v>
       </c>
       <c r="E4" s="3">
-        <v>0</v>
+        <v>11.0185</v>
       </c>
       <c r="F4" s="3">
-        <v>0</v>
+        <v>11.3207</v>
       </c>
       <c r="G4" s="3">
-        <v>0</v>
+        <v>10.467499999999999</v>
       </c>
       <c r="H4" s="4">
         <f>AVERAGE(Table1[[#This Row],[Tiempo1]:[Tiempo5]])</f>
-        <v>0</v>
+        <v>10.785340000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" s="2">
         <v>0.3</v>
       </c>
@@ -2519,7 +2520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" s="2">
         <v>0.4</v>
       </c>
@@ -2528,26 +2529,26 @@
         <v>40000</v>
       </c>
       <c r="C6" s="3">
-        <v>0</v>
+        <v>28.8857</v>
       </c>
       <c r="D6" s="3">
-        <v>0</v>
+        <v>26.563400000000001</v>
       </c>
       <c r="E6" s="3">
-        <v>0</v>
+        <v>28.469200000000001</v>
       </c>
       <c r="F6" s="3">
-        <v>0</v>
+        <v>27.441400000000002</v>
       </c>
       <c r="G6" s="3">
-        <v>0</v>
+        <v>26.504200000000001</v>
       </c>
       <c r="H6" s="4">
         <f>AVERAGE(Table1[[#This Row],[Tiempo1]:[Tiempo5]])</f>
-        <v>0</v>
+        <v>27.572780000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" s="2">
         <v>0.5</v>
       </c>
@@ -2575,7 +2576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="A8" s="2">
         <v>0.6</v>
       </c>
@@ -2584,26 +2585,26 @@
         <v>60000</v>
       </c>
       <c r="C8" s="3">
-        <v>0</v>
+        <v>51.407699999999998</v>
       </c>
       <c r="D8" s="3">
-        <v>0</v>
+        <v>51.375999999999998</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>52.207999999999998</v>
       </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>47.605499999999999</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>49.955800000000004</v>
       </c>
       <c r="H8" s="4">
         <f>AVERAGE(Table1[[#This Row],[Tiempo1]:[Tiempo5]])</f>
-        <v>0</v>
+        <v>50.510599999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9" s="2">
         <v>0.7</v>
       </c>
@@ -2631,7 +2632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10" s="2">
         <v>0.8</v>
       </c>
@@ -2640,26 +2641,27 @@
         <v>80000</v>
       </c>
       <c r="C10" s="3">
-        <v>0</v>
+        <v>85.055099999999996</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>81.126300000000001</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>83.186099999999996</v>
       </c>
       <c r="F10" s="3">
-        <v>0</v>
+        <v>83.730199999999996</v>
       </c>
       <c r="G10" s="3">
-        <v>0</v>
+        <v>81.845100000000002</v>
       </c>
       <c r="H10" s="4">
         <f>AVERAGE(Table1[[#This Row],[Tiempo1]:[Tiempo5]])</f>
-        <v>0</v>
-      </c>
+        <v>82.988560000000007</v>
+      </c>
+      <c r="I10" s="11"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11" s="2">
         <v>0.9</v>
       </c>
@@ -2687,7 +2689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:9">
       <c r="A12" s="2">
         <v>1</v>
       </c>
@@ -2696,26 +2698,26 @@
         <v>100000</v>
       </c>
       <c r="C12" s="3">
-        <v>0</v>
+        <v>127.274</v>
       </c>
       <c r="D12" s="3">
-        <v>0</v>
+        <v>117.783</v>
       </c>
       <c r="E12" s="3">
-        <v>0</v>
+        <v>141.31100000000001</v>
       </c>
       <c r="F12" s="3">
-        <v>0</v>
+        <v>120.93300000000001</v>
       </c>
       <c r="G12" s="3">
-        <v>0</v>
+        <v>131.47200000000001</v>
       </c>
       <c r="H12" s="4">
         <f>AVERAGE(Table1[[#This Row],[Tiempo1]:[Tiempo5]])</f>
-        <v>0</v>
+        <v>127.75460000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="4"/>
@@ -2725,7 +2727,7 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="15" spans="1:8" ht="14.25" customHeight="1">
+    <row r="15" spans="1:9" ht="14.25" customHeight="1">
       <c r="C15" s="10" t="s">
         <v>9</v>
       </c>
@@ -2735,7 +2737,7 @@
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
     </row>
-    <row r="16" spans="1:8" s="5" customFormat="1" ht="32">
+    <row r="16" spans="1:9" s="5" customFormat="1" ht="28">
       <c r="A16" s="4" t="s">
         <v>1</v>
       </c>
@@ -2761,7 +2763,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="5" customFormat="1">
+    <row r="17" spans="1:8" s="5" customFormat="1" ht="14">
       <c r="A17" s="2">
         <v>0.1</v>
       </c>
@@ -2789,7 +2791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="5" customFormat="1">
+    <row r="18" spans="1:8" s="5" customFormat="1" ht="14">
       <c r="A18" s="2">
         <v>0.2</v>
       </c>
@@ -3061,10 +3063,10 @@
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="61.83203125" customWidth="1"/>
-    <col min="2" max="2" width="90.5" customWidth="1"/>
+    <col min="1" max="1" width="61.81640625" customWidth="1"/>
+    <col min="2" max="2" width="90.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3099,12 +3101,116 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="85e30bcc-d76c-4413-8e4d-2dce22fb0743">
+      <UserInfo>
+        <DisplayName>Carlos Andres Lozano Garzon</DisplayName>
+        <AccountId>13</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Dario Ernesto Correal Torres</DisplayName>
+        <AccountId>15</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Mario  Fernando De la rosa Rosero</DisplayName>
+        <AccountId>16</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Christian Camilo Aparicio Baquen</DisplayName>
+        <AccountId>50</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Arturo Henao Chaparro</DisplayName>
+        <AccountId>48</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Luis Esteban Florez Salamanca</DisplayName>
+        <AccountId>33</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Ivan David Salazar Cardenas</DisplayName>
+        <AccountId>52</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Juan Carlos Marin Morales</DisplayName>
+        <AccountId>53</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Sofia Duque Gomez</DisplayName>
+        <AccountId>60</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Andres Felipe Romero Brand</DisplayName>
+        <AccountId>91</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Lindsay Vanessa Pinto Morato</DisplayName>
+        <AccountId>92</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Miguel Angel Acosta Walteros</DisplayName>
+        <AccountId>94</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Juan David Diaz Ipuz</DisplayName>
+        <AccountId>90</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Lily Aitana valentina Duque Chavez</DisplayName>
+        <AccountId>17</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Isaac David Bermudez Lara</DisplayName>
+        <AccountId>95</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Daniel Alejandro Angel Fuertes</DisplayName>
+        <AccountId>55</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jeniffer Liliam Mendoza Espinosa</DisplayName>
+        <AccountId>97</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Kevin Cohen Solano</DisplayName>
+        <AccountId>93</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Cesar Luis Moreno Gonzalez</DisplayName>
+        <AccountId>96</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jose Cristobal Arroyo Castellanos</DisplayName>
+        <AccountId>54</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="85e30bcc-d76c-4413-8e4d-2dce22fb0743" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="164883f8-7691-4ecf-b54a-664c0d0edefe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3357,122 +3463,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="85e30bcc-d76c-4413-8e4d-2dce22fb0743">
-      <UserInfo>
-        <DisplayName>Carlos Andres Lozano Garzon</DisplayName>
-        <AccountId>13</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Dario Ernesto Correal Torres</DisplayName>
-        <AccountId>15</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Mario  Fernando De la rosa Rosero</DisplayName>
-        <AccountId>16</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Christian Camilo Aparicio Baquen</DisplayName>
-        <AccountId>50</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Arturo Henao Chaparro</DisplayName>
-        <AccountId>48</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Luis Esteban Florez Salamanca</DisplayName>
-        <AccountId>33</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Ivan David Salazar Cardenas</DisplayName>
-        <AccountId>52</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Juan Carlos Marin Morales</DisplayName>
-        <AccountId>53</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Sofia Duque Gomez</DisplayName>
-        <AccountId>60</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Andres Felipe Romero Brand</DisplayName>
-        <AccountId>91</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Lindsay Vanessa Pinto Morato</DisplayName>
-        <AccountId>92</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Miguel Angel Acosta Walteros</DisplayName>
-        <AccountId>94</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Juan David Diaz Ipuz</DisplayName>
-        <AccountId>90</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Lily Aitana valentina Duque Chavez</DisplayName>
-        <AccountId>17</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Isaac David Bermudez Lara</DisplayName>
-        <AccountId>95</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Daniel Alejandro Angel Fuertes</DisplayName>
-        <AccountId>55</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jeniffer Liliam Mendoza Espinosa</DisplayName>
-        <AccountId>97</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Kevin Cohen Solano</DisplayName>
-        <AccountId>93</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Cesar Luis Moreno Gonzalez</DisplayName>
-        <AccountId>96</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jose Cristobal Arroyo Castellanos</DisplayName>
-        <AccountId>54</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="85e30bcc-d76c-4413-8e4d-2dce22fb0743" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="164883f8-7691-4ecf-b54a-664c0d0edefe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF3742-38F2-4B99-B335-CC4F04ED9F45}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C5E1E0-C817-4769-9D2D-1DC296B681FA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="85e30bcc-d76c-4413-8e4d-2dce22fb0743"/>
+    <ds:schemaRef ds:uri="164883f8-7691-4ecf-b54a-664c0d0edefe"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3497,12 +3502,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C5E1E0-C817-4769-9D2D-1DC296B681FA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF3742-38F2-4B99-B335-CC4F04ED9F45}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="85e30bcc-d76c-4413-8e4d-2dce22fb0743"/>
-    <ds:schemaRef ds:uri="164883f8-7691-4ecf-b54a-664c0d0edefe"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Docs/ISIS1225-TablasDatosReto2.xlsx
+++ b/Docs/ISIS1225-TablasDatosReto2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f37e920cb68ed4a8/Desktop/Reto2-G03/Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{4A5DBDDE-59DE-4983-A5DD-216DD4370536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CE162CA-726A-4580-81E1-998AC705562F}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{4A5DBDDE-59DE-4983-A5DD-216DD4370536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3F9D279-734E-4354-9D33-39B9177A17B5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
   </bookViews>
@@ -227,13 +227,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -893,31 +893,31 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.1147</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>9.3816000000000006</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>17.235299999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>28.8857</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>48.176900000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>51.407699999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>68.365899999999996</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>85.055099999999996</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>90.106300000000005</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>127.274</c:v>
@@ -2003,7 +2003,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="8674100" cy="6286500"/>
+    <xdr:ext cx="9296400" cy="6070600"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -2401,14 +2401,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.25" customHeight="1">
-      <c r="C1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="C1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:9" s="5" customFormat="1" ht="28">
       <c r="A2" s="4" t="s">
@@ -2445,23 +2445,23 @@
         <v>10000</v>
       </c>
       <c r="C3" s="3">
-        <v>0</v>
+        <v>0.1147</v>
       </c>
       <c r="D3" s="3">
-        <v>0</v>
+        <v>7.2500200000000001E-2</v>
       </c>
       <c r="E3" s="3">
-        <v>0</v>
+        <v>0.1249</v>
       </c>
       <c r="F3" s="3">
-        <v>0</v>
+        <v>0.1101</v>
       </c>
       <c r="G3" s="3">
-        <v>0</v>
+        <v>0.13919999999999999</v>
       </c>
       <c r="H3" s="4">
         <f>AVERAGE(Table1[[#This Row],[Tiempo1]:[Tiempo5]])</f>
-        <v>0</v>
+        <v>0.11228004</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="5" customFormat="1" ht="14">
@@ -2501,23 +2501,23 @@
         <v>30000</v>
       </c>
       <c r="C5" s="3">
-        <v>0</v>
+        <v>17.235299999999999</v>
       </c>
       <c r="D5" s="3">
-        <v>0</v>
+        <v>16.161000000000001</v>
       </c>
       <c r="E5" s="3">
-        <v>0</v>
+        <v>17.22</v>
       </c>
       <c r="F5" s="3">
-        <v>0</v>
+        <v>18.523</v>
       </c>
       <c r="G5" s="3">
-        <v>0</v>
+        <v>17.043299999999999</v>
       </c>
       <c r="H5" s="4">
         <f>AVERAGE(Table1[[#This Row],[Tiempo1]:[Tiempo5]])</f>
-        <v>0</v>
+        <v>17.236519999999999</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2557,23 +2557,23 @@
         <v>50000</v>
       </c>
       <c r="C7" s="3">
-        <v>0</v>
+        <v>48.176900000000003</v>
       </c>
       <c r="D7" s="3">
-        <v>0</v>
+        <v>47.979799999999997</v>
       </c>
       <c r="E7" s="3">
-        <v>0</v>
+        <v>50.816699999999997</v>
       </c>
       <c r="F7" s="3">
-        <v>0</v>
+        <v>47.734999999999999</v>
       </c>
       <c r="G7" s="3">
-        <v>0</v>
+        <v>46.3172</v>
       </c>
       <c r="H7" s="4">
         <f>AVERAGE(Table1[[#This Row],[Tiempo1]:[Tiempo5]])</f>
-        <v>0</v>
+        <v>48.205120000000001</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2613,23 +2613,23 @@
         <v>70000</v>
       </c>
       <c r="C9" s="3">
-        <v>0</v>
+        <v>68.365899999999996</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>66.650899999999993</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>67.638099999999994</v>
       </c>
       <c r="F9" s="3">
-        <v>0</v>
+        <v>64.061700099999996</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>66.135999999999996</v>
       </c>
       <c r="H9" s="4">
         <f>AVERAGE(Table1[[#This Row],[Tiempo1]:[Tiempo5]])</f>
-        <v>0</v>
+        <v>66.570520020000004</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2659,7 +2659,7 @@
         <f>AVERAGE(Table1[[#This Row],[Tiempo1]:[Tiempo5]])</f>
         <v>82.988560000000007</v>
       </c>
-      <c r="I10" s="11"/>
+      <c r="I10" s="9"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2">
@@ -2670,23 +2670,23 @@
         <v>90000</v>
       </c>
       <c r="C11" s="3">
-        <v>0</v>
+        <v>90.106300000000005</v>
       </c>
       <c r="D11" s="3">
-        <v>0</v>
+        <v>89.195300000000003</v>
       </c>
       <c r="E11" s="3">
-        <v>0</v>
+        <v>87.213399999999993</v>
       </c>
       <c r="F11" s="3">
-        <v>0</v>
+        <v>88.127799999999993</v>
       </c>
       <c r="G11" s="3">
-        <v>0</v>
+        <v>100.12730000000001</v>
       </c>
       <c r="H11" s="4">
         <f>AVERAGE(Table1[[#This Row],[Tiempo1]:[Tiempo5]])</f>
-        <v>0</v>
+        <v>90.954019999999986</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2728,14 +2728,14 @@
       <c r="H13" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="14.25" customHeight="1">
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
     </row>
     <row r="16" spans="1:9" s="5" customFormat="1" ht="28">
       <c r="A16" s="4" t="s">
@@ -3101,116 +3101,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="85e30bcc-d76c-4413-8e4d-2dce22fb0743">
-      <UserInfo>
-        <DisplayName>Carlos Andres Lozano Garzon</DisplayName>
-        <AccountId>13</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Dario Ernesto Correal Torres</DisplayName>
-        <AccountId>15</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Mario  Fernando De la rosa Rosero</DisplayName>
-        <AccountId>16</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Christian Camilo Aparicio Baquen</DisplayName>
-        <AccountId>50</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Arturo Henao Chaparro</DisplayName>
-        <AccountId>48</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Luis Esteban Florez Salamanca</DisplayName>
-        <AccountId>33</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Ivan David Salazar Cardenas</DisplayName>
-        <AccountId>52</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Juan Carlos Marin Morales</DisplayName>
-        <AccountId>53</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Sofia Duque Gomez</DisplayName>
-        <AccountId>60</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Andres Felipe Romero Brand</DisplayName>
-        <AccountId>91</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Lindsay Vanessa Pinto Morato</DisplayName>
-        <AccountId>92</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Miguel Angel Acosta Walteros</DisplayName>
-        <AccountId>94</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Juan David Diaz Ipuz</DisplayName>
-        <AccountId>90</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Lily Aitana valentina Duque Chavez</DisplayName>
-        <AccountId>17</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Isaac David Bermudez Lara</DisplayName>
-        <AccountId>95</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Daniel Alejandro Angel Fuertes</DisplayName>
-        <AccountId>55</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jeniffer Liliam Mendoza Espinosa</DisplayName>
-        <AccountId>97</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Kevin Cohen Solano</DisplayName>
-        <AccountId>93</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Cesar Luis Moreno Gonzalez</DisplayName>
-        <AccountId>96</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jose Cristobal Arroyo Castellanos</DisplayName>
-        <AccountId>54</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="85e30bcc-d76c-4413-8e4d-2dce22fb0743" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="164883f8-7691-4ecf-b54a-664c0d0edefe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3463,21 +3359,122 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="85e30bcc-d76c-4413-8e4d-2dce22fb0743">
+      <UserInfo>
+        <DisplayName>Carlos Andres Lozano Garzon</DisplayName>
+        <AccountId>13</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Dario Ernesto Correal Torres</DisplayName>
+        <AccountId>15</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Mario  Fernando De la rosa Rosero</DisplayName>
+        <AccountId>16</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Christian Camilo Aparicio Baquen</DisplayName>
+        <AccountId>50</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Arturo Henao Chaparro</DisplayName>
+        <AccountId>48</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Luis Esteban Florez Salamanca</DisplayName>
+        <AccountId>33</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Ivan David Salazar Cardenas</DisplayName>
+        <AccountId>52</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Juan Carlos Marin Morales</DisplayName>
+        <AccountId>53</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Sofia Duque Gomez</DisplayName>
+        <AccountId>60</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Andres Felipe Romero Brand</DisplayName>
+        <AccountId>91</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Lindsay Vanessa Pinto Morato</DisplayName>
+        <AccountId>92</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Miguel Angel Acosta Walteros</DisplayName>
+        <AccountId>94</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Juan David Diaz Ipuz</DisplayName>
+        <AccountId>90</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Lily Aitana valentina Duque Chavez</DisplayName>
+        <AccountId>17</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Isaac David Bermudez Lara</DisplayName>
+        <AccountId>95</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Daniel Alejandro Angel Fuertes</DisplayName>
+        <AccountId>55</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jeniffer Liliam Mendoza Espinosa</DisplayName>
+        <AccountId>97</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Kevin Cohen Solano</DisplayName>
+        <AccountId>93</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Cesar Luis Moreno Gonzalez</DisplayName>
+        <AccountId>96</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jose Cristobal Arroyo Castellanos</DisplayName>
+        <AccountId>54</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="85e30bcc-d76c-4413-8e4d-2dce22fb0743" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="164883f8-7691-4ecf-b54a-664c0d0edefe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C5E1E0-C817-4769-9D2D-1DC296B681FA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF3742-38F2-4B99-B335-CC4F04ED9F45}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="85e30bcc-d76c-4413-8e4d-2dce22fb0743"/>
-    <ds:schemaRef ds:uri="164883f8-7691-4ecf-b54a-664c0d0edefe"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3502,9 +3499,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF3742-38F2-4B99-B335-CC4F04ED9F45}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C5E1E0-C817-4769-9D2D-1DC296B681FA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="85e30bcc-d76c-4413-8e4d-2dce22fb0743"/>
+    <ds:schemaRef ds:uri="164883f8-7691-4ecf-b54a-664c0d0edefe"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Docs/ISIS1225-TablasDatosReto2.xlsx
+++ b/Docs/ISIS1225-TablasDatosReto2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f37e920cb68ed4a8/Desktop/Reto2-G03/Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{4A5DBDDE-59DE-4983-A5DD-216DD4370536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3F9D279-734E-4354-9D33-39B9177A17B5}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{4A5DBDDE-59DE-4983-A5DD-216DD4370536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FED316B5-EBB6-4662-8D56-60A44B29479C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
   </bookViews>
@@ -1069,31 +1069,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>4.3148999214172319</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>6.1424201011657686</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>6.1981198310851999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>8.6322199821472143</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>10.21958003044127</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>11.634040021896318</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>13.982019996643022</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>13.683559942245441</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>17.169700002670218</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2395,7 +2395,7 @@
     <col min="1" max="1" width="19.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="12" width="24.453125" customWidth="1"/>
   </cols>
@@ -2800,23 +2800,23 @@
         <v>20000</v>
       </c>
       <c r="C18" s="3">
-        <v>0</v>
+        <v>3.9840998649597101</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
+        <v>4.8567998409271196</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>4.5381000041961599</v>
       </c>
       <c r="F18" s="3">
-        <v>0</v>
+        <v>4.1802999973297101</v>
       </c>
       <c r="G18" s="3">
-        <v>0</v>
+        <v>4.0151998996734601</v>
       </c>
       <c r="H18" s="4">
         <f>AVERAGE(Table13[[#This Row],[Tiempo 1]:[Tiempo 5]])</f>
-        <v>0</v>
+        <v>4.3148999214172319</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2828,23 +2828,23 @@
         <v>30000</v>
       </c>
       <c r="C19" s="3">
-        <v>0</v>
+        <v>6.2367999553680402</v>
       </c>
       <c r="D19" s="3">
-        <v>0</v>
+        <v>6.29010009765625</v>
       </c>
       <c r="E19" s="3">
-        <v>0</v>
+        <v>6.2019002437591499</v>
       </c>
       <c r="F19" s="3">
-        <v>0</v>
+        <v>5.9577002525329501</v>
       </c>
       <c r="G19" s="3">
-        <v>0</v>
+        <v>6.0255999565124503</v>
       </c>
       <c r="H19" s="4">
         <f>AVERAGE(Table13[[#This Row],[Tiempo 1]:[Tiempo 5]])</f>
-        <v>0</v>
+        <v>6.1424201011657686</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2856,23 +2856,23 @@
         <v>40000</v>
       </c>
       <c r="C20" s="3">
-        <v>0</v>
+        <v>5.7714996337890598</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>6.2012999057769704</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>6.5951998233795104</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>6.1326999664306596</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>6.2898998260498002</v>
       </c>
       <c r="H20" s="4">
         <f>AVERAGE(Table13[[#This Row],[Tiempo 1]:[Tiempo 5]])</f>
-        <v>0</v>
+        <v>6.1981198310851999</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2884,23 +2884,23 @@
         <v>50000</v>
       </c>
       <c r="C21" s="3">
-        <v>0</v>
+        <v>7.7952001094818097</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>8.6152000427246094</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>9.1731998920440603</v>
       </c>
       <c r="F21" s="3">
-        <v>0</v>
+        <v>9.1158998012542707</v>
       </c>
       <c r="G21" s="3">
-        <v>0</v>
+        <v>8.4616000652313197</v>
       </c>
       <c r="H21" s="4">
         <f>AVERAGE(Table13[[#This Row],[Tiempo 1]:[Tiempo 5]])</f>
-        <v>0</v>
+        <v>8.6322199821472143</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -2912,23 +2912,23 @@
         <v>60000</v>
       </c>
       <c r="C22" s="3">
-        <v>0</v>
+        <v>8.6030998229980398</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>10.4917001724243</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>10.7696998119354</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>11.457000255584701</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>9.7764000892639107</v>
       </c>
       <c r="H22" s="4">
         <f>AVERAGE(Table13[[#This Row],[Tiempo 1]:[Tiempo 5]])</f>
-        <v>0</v>
+        <v>10.21958003044127</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -2940,23 +2940,23 @@
         <v>70000</v>
       </c>
       <c r="C23" s="3">
-        <v>0</v>
+        <v>11.468099832534699</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>11.4037001132965</v>
       </c>
       <c r="E23" s="3">
-        <v>0</v>
+        <v>11.5676999092102</v>
       </c>
       <c r="F23" s="3">
-        <v>0</v>
+        <v>11.6924002170562</v>
       </c>
       <c r="G23" s="3">
-        <v>0</v>
+        <v>12.038300037383999</v>
       </c>
       <c r="H23" s="4">
         <f>AVERAGE(Table13[[#This Row],[Tiempo 1]:[Tiempo 5]])</f>
-        <v>0</v>
+        <v>11.634040021896318</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -2968,23 +2968,23 @@
         <v>80000</v>
       </c>
       <c r="C24" s="3">
-        <v>0</v>
+        <v>13.178200244903501</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>15.4297997951507</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>13.221599817275999</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>13.305999994277901</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>14.774500131607001</v>
       </c>
       <c r="H24" s="4">
         <f>AVERAGE(Table13[[#This Row],[Tiempo 1]:[Tiempo 5]])</f>
-        <v>0</v>
+        <v>13.982019996643022</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -2996,23 +2996,23 @@
         <v>90000</v>
       </c>
       <c r="C25" s="3">
-        <v>0</v>
+        <v>13.598699808120699</v>
       </c>
       <c r="D25" s="3">
-        <v>0</v>
+        <v>13.616600036621</v>
       </c>
       <c r="E25" s="3">
-        <v>0</v>
+        <v>13.5401000976562</v>
       </c>
       <c r="F25" s="3">
-        <v>0</v>
+        <v>13.613499879837001</v>
       </c>
       <c r="G25" s="3">
-        <v>0</v>
+        <v>14.048899888992301</v>
       </c>
       <c r="H25" s="4">
         <f>AVERAGE(Table13[[#This Row],[Tiempo 1]:[Tiempo 5]])</f>
-        <v>0</v>
+        <v>13.683559942245441</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3024,23 +3024,23 @@
         <v>100000</v>
       </c>
       <c r="C26" s="3">
-        <v>0</v>
+        <v>15.988400220870901</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>18.136799812316799</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
+        <v>16.9165999889373</v>
       </c>
       <c r="F26" s="3">
-        <v>0</v>
+        <v>16.169800043106001</v>
       </c>
       <c r="G26" s="3">
-        <v>0</v>
+        <v>18.636899948120099</v>
       </c>
       <c r="H26" s="4">
         <f>AVERAGE(Table13[[#This Row],[Tiempo 1]:[Tiempo 5]])</f>
-        <v>0</v>
+        <v>17.169700002670218</v>
       </c>
     </row>
   </sheetData>
@@ -3101,12 +3101,116 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="85e30bcc-d76c-4413-8e4d-2dce22fb0743">
+      <UserInfo>
+        <DisplayName>Carlos Andres Lozano Garzon</DisplayName>
+        <AccountId>13</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Dario Ernesto Correal Torres</DisplayName>
+        <AccountId>15</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Mario  Fernando De la rosa Rosero</DisplayName>
+        <AccountId>16</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Christian Camilo Aparicio Baquen</DisplayName>
+        <AccountId>50</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Arturo Henao Chaparro</DisplayName>
+        <AccountId>48</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Luis Esteban Florez Salamanca</DisplayName>
+        <AccountId>33</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Ivan David Salazar Cardenas</DisplayName>
+        <AccountId>52</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Juan Carlos Marin Morales</DisplayName>
+        <AccountId>53</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Sofia Duque Gomez</DisplayName>
+        <AccountId>60</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Andres Felipe Romero Brand</DisplayName>
+        <AccountId>91</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Lindsay Vanessa Pinto Morato</DisplayName>
+        <AccountId>92</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Miguel Angel Acosta Walteros</DisplayName>
+        <AccountId>94</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Juan David Diaz Ipuz</DisplayName>
+        <AccountId>90</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Lily Aitana valentina Duque Chavez</DisplayName>
+        <AccountId>17</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Isaac David Bermudez Lara</DisplayName>
+        <AccountId>95</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Daniel Alejandro Angel Fuertes</DisplayName>
+        <AccountId>55</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jeniffer Liliam Mendoza Espinosa</DisplayName>
+        <AccountId>97</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Kevin Cohen Solano</DisplayName>
+        <AccountId>93</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Cesar Luis Moreno Gonzalez</DisplayName>
+        <AccountId>96</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jose Cristobal Arroyo Castellanos</DisplayName>
+        <AccountId>54</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="85e30bcc-d76c-4413-8e4d-2dce22fb0743" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="164883f8-7691-4ecf-b54a-664c0d0edefe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3359,122 +3463,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="85e30bcc-d76c-4413-8e4d-2dce22fb0743">
-      <UserInfo>
-        <DisplayName>Carlos Andres Lozano Garzon</DisplayName>
-        <AccountId>13</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Dario Ernesto Correal Torres</DisplayName>
-        <AccountId>15</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Mario  Fernando De la rosa Rosero</DisplayName>
-        <AccountId>16</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Christian Camilo Aparicio Baquen</DisplayName>
-        <AccountId>50</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Arturo Henao Chaparro</DisplayName>
-        <AccountId>48</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Luis Esteban Florez Salamanca</DisplayName>
-        <AccountId>33</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Ivan David Salazar Cardenas</DisplayName>
-        <AccountId>52</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Juan Carlos Marin Morales</DisplayName>
-        <AccountId>53</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Sofia Duque Gomez</DisplayName>
-        <AccountId>60</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Andres Felipe Romero Brand</DisplayName>
-        <AccountId>91</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Lindsay Vanessa Pinto Morato</DisplayName>
-        <AccountId>92</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Miguel Angel Acosta Walteros</DisplayName>
-        <AccountId>94</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Juan David Diaz Ipuz</DisplayName>
-        <AccountId>90</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Lily Aitana valentina Duque Chavez</DisplayName>
-        <AccountId>17</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Isaac David Bermudez Lara</DisplayName>
-        <AccountId>95</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Daniel Alejandro Angel Fuertes</DisplayName>
-        <AccountId>55</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jeniffer Liliam Mendoza Espinosa</DisplayName>
-        <AccountId>97</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Kevin Cohen Solano</DisplayName>
-        <AccountId>93</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Cesar Luis Moreno Gonzalez</DisplayName>
-        <AccountId>96</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jose Cristobal Arroyo Castellanos</DisplayName>
-        <AccountId>54</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="85e30bcc-d76c-4413-8e4d-2dce22fb0743" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="164883f8-7691-4ecf-b54a-664c0d0edefe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF3742-38F2-4B99-B335-CC4F04ED9F45}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C5E1E0-C817-4769-9D2D-1DC296B681FA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="85e30bcc-d76c-4413-8e4d-2dce22fb0743"/>
+    <ds:schemaRef ds:uri="164883f8-7691-4ecf-b54a-664c0d0edefe"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3499,12 +3502,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C5E1E0-C817-4769-9D2D-1DC296B681FA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF3742-38F2-4B99-B335-CC4F04ED9F45}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="85e30bcc-d76c-4413-8e4d-2dce22fb0743"/>
-    <ds:schemaRef ds:uri="164883f8-7691-4ecf-b54a-664c0d0edefe"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Docs/ISIS1225-TablasDatosReto2.xlsx
+++ b/Docs/ISIS1225-TablasDatosReto2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f37e920cb68ed4a8/Desktop/Reto2-G03/Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{4A5DBDDE-59DE-4983-A5DD-216DD4370536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FED316B5-EBB6-4662-8D56-60A44B29479C}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{4A5DBDDE-59DE-4983-A5DD-216DD4370536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2F97CF6-5D2C-425B-9059-ECEFE83D5CA3}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
   </bookViews>
   <sheets>
     <sheet name="01-Data Req. 4" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>TIEMPOS PARA REQUERIMIENTO 4 - RETO 1</t>
   </si>
@@ -93,6 +93,15 @@
   </si>
   <si>
     <t>A partir del análisis teórico y experimental realizado, ¿qué conclusión puede obtener sobre el impacto de la estructura de datos en el rendimiento de un algoritmo? ¿Es importante la selección de una estructura de datos específica según el tipo de requerimiento?</t>
+  </si>
+  <si>
+    <t>Los tiempos del requerimento 4 en el reto 2 son ampliamente menores, ya que la complejidad para encontrar los datos es de O(1), mientras que con los ordenamientos son de O(N)</t>
+  </si>
+  <si>
+    <t>En la teoria deben ser las tablas de hash por su complejidad, en nuestro caso se comprobó que fue más rápido en tablas de hash y con estos resultados nuestra conclusión es que llega a ser más eficiente entre más grande sea el tamaño del archivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El impacto es significativamente importante, ya que sin el hashing el tiempo crecia de manera exponencial, y con el hashing se mantuvo en un crecimiento leve, es decir con una menor demora </t>
   </si>
 </sst>
 </file>
@@ -207,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -233,6 +242,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1066,7 +1078,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>5.5020141601562447E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>4.3148999214172319</c:v>
@@ -2772,23 +2784,23 @@
         <v>10000</v>
       </c>
       <c r="C17" s="3">
-        <v>0</v>
+        <v>5.83002567291259E-2</v>
       </c>
       <c r="D17" s="3">
-        <v>0</v>
+        <v>6.3899993896484306E-2</v>
       </c>
       <c r="E17" s="3">
-        <v>0</v>
+        <v>5.1600217819213798E-2</v>
       </c>
       <c r="F17" s="3">
-        <v>0</v>
+        <v>5.52999973297119E-2</v>
       </c>
       <c r="G17" s="3">
-        <v>0</v>
+        <v>4.6000242233276298E-2</v>
       </c>
       <c r="H17" s="4">
         <f>AVERAGE(Table13[[#This Row],[Tiempo 1]:[Tiempo 5]])</f>
-        <v>0</v>
+        <v>5.5020141601562447E-2</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="5" customFormat="1" ht="14">
@@ -3081,19 +3093,25 @@
       <c r="A2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="7"/>
+      <c r="B2" s="12" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="3" spans="1:2" ht="110" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="7"/>
+      <c r="B3" s="12" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="4" spans="1:2" ht="110" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="7"/>
+      <c r="B4" s="12" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
